--- a/Online Assessment 0/web_resources/Data files for Assessments/Online Assessment 0/Data3_7.xlsx
+++ b/Online Assessment 0/web_resources/Data files for Assessments/Online Assessment 0/Data3_7.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C101"/>
+  <dimension ref="A1:C201"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -362,12 +362,12 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>IVCat</t>
+          <t>Treatment3</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Response</t>
+          <t>Interesting</t>
         </is>
       </c>
     </row>
@@ -378,10 +378,10 @@
         </is>
       </c>
       <c r="B2">
-        <v>0.3314476586720206</v>
+        <v>0.2668891009457917</v>
       </c>
       <c r="C2">
-        <v>1.692300402424471</v>
+        <v>-0.556933104761276</v>
       </c>
     </row>
     <row r="3">
@@ -391,10 +391,10 @@
         </is>
       </c>
       <c r="B3">
-        <v>0.05361083165974721</v>
+        <v>-0.4800680815237507</v>
       </c>
       <c r="C3">
-        <v>0.8759272016609165</v>
+        <v>-0.996949646706489</v>
       </c>
     </row>
     <row r="4">
@@ -404,10 +404,10 @@
         </is>
       </c>
       <c r="B4">
-        <v>0.855188560498011</v>
+        <v>0.2589625559946802</v>
       </c>
       <c r="C4">
-        <v>0.5985447114872123</v>
+        <v>-0.9772552943222268</v>
       </c>
     </row>
     <row r="5">
@@ -417,10 +417,10 @@
         </is>
       </c>
       <c r="B5">
-        <v>0.4092959420862265</v>
+        <v>-0.3179274070993474</v>
       </c>
       <c r="C5">
-        <v>0.6278427584965121</v>
+        <v>-0.9496922255388134</v>
       </c>
     </row>
     <row r="6">
@@ -430,10 +430,10 @@
         </is>
       </c>
       <c r="B6">
-        <v>-0.3013723600598748</v>
+        <v>0.2031349900474687</v>
       </c>
       <c r="C6">
-        <v>1.721620257829759</v>
+        <v>0.3115872683003984</v>
       </c>
     </row>
     <row r="7">
@@ -443,10 +443,10 @@
         </is>
       </c>
       <c r="B7">
-        <v>0.7505011656619309</v>
+        <v>1.215846025806691</v>
       </c>
       <c r="C7">
-        <v>1.58594908795602</v>
+        <v>-0.4263525039891611</v>
       </c>
     </row>
     <row r="8">
@@ -456,10 +456,10 @@
         </is>
       </c>
       <c r="B8">
-        <v>0.1566583028842413</v>
+        <v>-1.535114035935721</v>
       </c>
       <c r="C8">
-        <v>0.05389493094862544</v>
+        <v>-0.7159368312397479</v>
       </c>
     </row>
     <row r="9">
@@ -469,10 +469,10 @@
         </is>
       </c>
       <c r="B9">
-        <v>1.54083808567202</v>
+        <v>-1.469436663106269</v>
       </c>
       <c r="C9">
-        <v>0.3302686716455926</v>
+        <v>-1.519324064258298</v>
       </c>
     </row>
     <row r="10">
@@ -482,10 +482,10 @@
         </is>
       </c>
       <c r="B10">
-        <v>2.046537961569899</v>
+        <v>-0.853481842602246</v>
       </c>
       <c r="C10">
-        <v>0.7488216668076</v>
+        <v>-1.960237884963997</v>
       </c>
     </row>
     <row r="11">
@@ -495,10 +495,10 @@
         </is>
       </c>
       <c r="B11">
-        <v>-1.072428583818289</v>
+        <v>-1.040159104782129</v>
       </c>
       <c r="C11">
-        <v>-0.7511201561104199</v>
+        <v>0.271514581216003</v>
       </c>
     </row>
     <row r="12">
@@ -508,10 +508,10 @@
         </is>
       </c>
       <c r="B12">
-        <v>0.4794617927949125</v>
+        <v>-0.4109277807866417</v>
       </c>
       <c r="C12">
-        <v>-0.5264517631934857</v>
+        <v>-0.6160506646104476</v>
       </c>
     </row>
     <row r="13">
@@ -521,10 +521,10 @@
         </is>
       </c>
       <c r="B13">
-        <v>-0.1431117935479551</v>
+        <v>-0.5594768852484888</v>
       </c>
       <c r="C13">
-        <v>0.3316834820614382</v>
+        <v>0.1814629094609324</v>
       </c>
     </row>
     <row r="14">
@@ -534,10 +534,10 @@
         </is>
       </c>
       <c r="B14">
-        <v>-0.2816062421443302</v>
+        <v>-1.904278780767509</v>
       </c>
       <c r="C14">
-        <v>0.3663733831146055</v>
+        <v>-0.05564083337243875</v>
       </c>
     </row>
     <row r="15">
@@ -547,10 +547,10 @@
         </is>
       </c>
       <c r="B15">
-        <v>-0.5250627270169</v>
+        <v>-1.026159074310303</v>
       </c>
       <c r="C15">
-        <v>-1.888656102531438</v>
+        <v>1.837326152425018</v>
       </c>
     </row>
     <row r="16">
@@ -560,10 +560,10 @@
         </is>
       </c>
       <c r="B16">
-        <v>0.4216469933317233</v>
+        <v>-1.629085201408575</v>
       </c>
       <c r="C16">
-        <v>-0.6438856223525236</v>
+        <v>-0.4780933789090573</v>
       </c>
     </row>
     <row r="17">
@@ -573,10 +573,10 @@
         </is>
       </c>
       <c r="B17">
-        <v>-0.4048111815028915</v>
+        <v>1.339807520586277</v>
       </c>
       <c r="C17">
-        <v>-0.3067408814064758</v>
+        <v>0.1892088721834559</v>
       </c>
     </row>
     <row r="18">
@@ -586,10 +586,10 @@
         </is>
       </c>
       <c r="B18">
-        <v>1.3834362284775</v>
+        <v>1.643966505882117</v>
       </c>
       <c r="C18">
-        <v>-0.05166508889363663</v>
+        <v>0.6815487608869188</v>
       </c>
     </row>
     <row r="19">
@@ -599,10 +599,10 @@
         </is>
       </c>
       <c r="B19">
-        <v>2.011970059486202</v>
+        <v>1.012556090474767</v>
       </c>
       <c r="C19">
-        <v>1.092409918580965</v>
+        <v>0.5260692135891025</v>
       </c>
     </row>
     <row r="20">
@@ -612,10 +612,10 @@
         </is>
       </c>
       <c r="B20">
-        <v>-0.7266291842462503</v>
+        <v>0.1116944555404423</v>
       </c>
       <c r="C20">
-        <v>-1.386925171166849</v>
+        <v>1.676580503027832</v>
       </c>
     </row>
     <row r="21">
@@ -625,10 +625,10 @@
         </is>
       </c>
       <c r="B21">
-        <v>0.6125044298205983</v>
+        <v>0.4113159684215923</v>
       </c>
       <c r="C21">
-        <v>-0.1353781559627417</v>
+        <v>0.07844512180868328</v>
       </c>
     </row>
     <row r="22">
@@ -638,10 +638,10 @@
         </is>
       </c>
       <c r="B22">
-        <v>-0.4887295193266008</v>
+        <v>1.214148362262075</v>
       </c>
       <c r="C22">
-        <v>-0.3106999028047377</v>
+        <v>1.849398132373948</v>
       </c>
     </row>
     <row r="23">
@@ -651,10 +651,10 @@
         </is>
       </c>
       <c r="B23">
-        <v>-0.6169586413568018</v>
+        <v>0.9438963712315159</v>
       </c>
       <c r="C23">
-        <v>-0.5911567546681883</v>
+        <v>-0.7339941715083712</v>
       </c>
     </row>
     <row r="24">
@@ -664,10 +664,10 @@
         </is>
       </c>
       <c r="B24">
-        <v>0.07635379939594558</v>
+        <v>-0.1923376629325724</v>
       </c>
       <c r="C24">
-        <v>-0.8561442530205802</v>
+        <v>-0.2803043214807509</v>
       </c>
     </row>
     <row r="25">
@@ -677,10 +677,10 @@
         </is>
       </c>
       <c r="B25">
-        <v>0.339076852290011</v>
+        <v>1.764045521317776</v>
       </c>
       <c r="C25">
-        <v>-0.9225796402207884</v>
+        <v>1.507394201089754</v>
       </c>
     </row>
     <row r="26">
@@ -690,10 +690,10 @@
         </is>
       </c>
       <c r="B26">
-        <v>0.124033696478516</v>
+        <v>0.9817686308251192</v>
       </c>
       <c r="C26">
-        <v>-0.07422891848133228</v>
+        <v>0.4445421259970428</v>
       </c>
     </row>
     <row r="27">
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="B27">
-        <v>0.002669547841912649</v>
+        <v>-1.121495896079659</v>
       </c>
       <c r="C27">
-        <v>-0.6543125665982792</v>
+        <v>0.8500906854440102</v>
       </c>
     </row>
     <row r="28">
@@ -716,10 +716,10 @@
         </is>
       </c>
       <c r="B28">
-        <v>1.351543492514479</v>
+        <v>0.02027789567858817</v>
       </c>
       <c r="C28">
-        <v>-0.3971990208381354</v>
+        <v>-0.8214518349484584</v>
       </c>
     </row>
     <row r="29">
@@ -729,10 +729,10 @@
         </is>
       </c>
       <c r="B29">
-        <v>-0.4320162541305106</v>
+        <v>-1.552172661280745</v>
       </c>
       <c r="C29">
-        <v>-1.331840998803201</v>
+        <v>0.5705093803651274</v>
       </c>
     </row>
     <row r="30">
@@ -742,10 +742,10 @@
         </is>
       </c>
       <c r="B30">
-        <v>0.6393309627417954</v>
+        <v>-0.9399444569401282</v>
       </c>
       <c r="C30">
-        <v>0.7286814872414273</v>
+        <v>-0.8651874863614435</v>
       </c>
     </row>
     <row r="31">
@@ -755,10 +755,10 @@
         </is>
       </c>
       <c r="B31">
-        <v>1.08503475341436</v>
+        <v>-0.4202630577673812</v>
       </c>
       <c r="C31">
-        <v>2.944084869060137</v>
+        <v>0.9381839481778899</v>
       </c>
     </row>
     <row r="32">
@@ -768,10 +768,10 @@
         </is>
       </c>
       <c r="B32">
-        <v>-0.5746024671708952</v>
+        <v>-0.6323881590874305</v>
       </c>
       <c r="C32">
-        <v>0.1740189839787845</v>
+        <v>-0.5532866777956755</v>
       </c>
     </row>
     <row r="33">
@@ -781,10 +781,10 @@
         </is>
       </c>
       <c r="B33">
-        <v>0.2045315636478936</v>
+        <v>-1.316014526705893</v>
       </c>
       <c r="C33">
-        <v>0.1369822389645417</v>
+        <v>0.2712623004877468</v>
       </c>
     </row>
     <row r="34">
@@ -794,10 +794,10 @@
         </is>
       </c>
       <c r="B34">
-        <v>-0.2471070546121142</v>
+        <v>0.9113596903471807</v>
       </c>
       <c r="C34">
-        <v>1.797601300236695</v>
+        <v>-0.1854509538000992</v>
       </c>
     </row>
     <row r="35">
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="B35">
-        <v>-1.965433599022266</v>
+        <v>-2.199948694659928</v>
       </c>
       <c r="C35">
-        <v>-1.777258296348562</v>
+        <v>-1.688612127213737</v>
       </c>
     </row>
     <row r="36">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="B36">
-        <v>0.9085483239549875</v>
+        <v>0.2039804065545587</v>
       </c>
       <c r="C36">
-        <v>0.2205876789219059</v>
+        <v>0.5445007315367661</v>
       </c>
     </row>
     <row r="37">
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c r="B37">
-        <v>-0.0899281112685979</v>
+        <v>0.2187674702736952</v>
       </c>
       <c r="C37">
-        <v>1.175324049642194</v>
+        <v>0.6238454874684778</v>
       </c>
     </row>
     <row r="38">
@@ -846,10 +846,10 @@
         </is>
       </c>
       <c r="B38">
-        <v>-1.425097275292743</v>
+        <v>-0.5436605870284054</v>
       </c>
       <c r="C38">
-        <v>-0.8750995814724444</v>
+        <v>-0.9241739910784461</v>
       </c>
     </row>
     <row r="39">
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="B39">
-        <v>-1.151206920767745</v>
+        <v>1.15385258294466</v>
       </c>
       <c r="C39">
-        <v>0.0310382799223447</v>
+        <v>1.521540630036867</v>
       </c>
     </row>
     <row r="40">
@@ -872,10 +872,10 @@
         </is>
       </c>
       <c r="B40">
-        <v>0.9661953245593421</v>
+        <v>-0.7146966616211365</v>
       </c>
       <c r="C40">
-        <v>0.495695717141595</v>
+        <v>-0.04171855229192417</v>
       </c>
     </row>
     <row r="41">
@@ -885,10 +885,10 @@
         </is>
       </c>
       <c r="B41">
-        <v>0.6057904793207134</v>
+        <v>2.673983824095672</v>
       </c>
       <c r="C41">
-        <v>0.5184430452580548</v>
+        <v>1.111303486007547</v>
       </c>
     </row>
     <row r="42">
@@ -898,10 +898,10 @@
         </is>
       </c>
       <c r="B42">
-        <v>0.07579746731801265</v>
+        <v>-0.2870067946806898</v>
       </c>
       <c r="C42">
-        <v>-1.804057269212477</v>
+        <v>1.656770160698936</v>
       </c>
     </row>
     <row r="43">
@@ -911,10 +911,10 @@
         </is>
       </c>
       <c r="B43">
-        <v>-1.045856171262294</v>
+        <v>0.6958834483994623</v>
       </c>
       <c r="C43">
-        <v>-0.9681853749734347</v>
+        <v>0.7236434884479587</v>
       </c>
     </row>
     <row r="44">
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="B44">
-        <v>-0.03211685061361106</v>
+        <v>0.6720443369939263</v>
       </c>
       <c r="C44">
-        <v>-1.392976535260772</v>
+        <v>-0.272906748502708</v>
       </c>
     </row>
     <row r="45">
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="B45">
-        <v>1.443037100773248</v>
+        <v>0.6801494037263325</v>
       </c>
       <c r="C45">
-        <v>-0.06733616032318657</v>
+        <v>0.1957978881633623</v>
       </c>
     </row>
     <row r="46">
@@ -950,10 +950,10 @@
         </is>
       </c>
       <c r="B46">
-        <v>0.3184036460528155</v>
+        <v>-0.8650219277536243</v>
       </c>
       <c r="C46">
-        <v>0.542066661610232</v>
+        <v>-0.5096449520763984</v>
       </c>
     </row>
     <row r="47">
@@ -963,10 +963,10 @@
         </is>
       </c>
       <c r="B47">
-        <v>-0.298415017057456</v>
+        <v>-0.5876438543776366</v>
       </c>
       <c r="C47">
-        <v>-0.07049042873899933</v>
+        <v>0.2874174471293452</v>
       </c>
     </row>
     <row r="48">
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="B48">
-        <v>0.02061203016495712</v>
+        <v>-0.4781623734136818</v>
       </c>
       <c r="C48">
-        <v>0.5874892199826196</v>
+        <v>-0.7360724210084495</v>
       </c>
     </row>
     <row r="49">
@@ -989,10 +989,10 @@
         </is>
       </c>
       <c r="B49">
-        <v>1.247162907880165</v>
+        <v>-0.7769973640431925</v>
       </c>
       <c r="C49">
-        <v>1.769773179513288</v>
+        <v>-0.2647956214672279</v>
       </c>
     </row>
     <row r="50">
@@ -1002,10 +1002,10 @@
         </is>
       </c>
       <c r="B50">
-        <v>-0.7931787434569266</v>
+        <v>0.1504712366809087</v>
       </c>
       <c r="C50">
-        <v>0.05003250171338947</v>
+        <v>-0.5225501052084307</v>
       </c>
     </row>
     <row r="51">
@@ -1015,10 +1015,10 @@
         </is>
       </c>
       <c r="B51">
-        <v>-0.2214002857670098</v>
+        <v>0.2072769484996772</v>
       </c>
       <c r="C51">
-        <v>0.0331217294677621</v>
+        <v>0.2048498856992413</v>
       </c>
     </row>
     <row r="52">
@@ -1028,10 +1028,10 @@
         </is>
       </c>
       <c r="B52">
-        <v>-0.931072983489994</v>
+        <v>-0.6687586840457632</v>
       </c>
       <c r="C52">
-        <v>0.02432633042447535</v>
+        <v>-0.6356167725348146</v>
       </c>
     </row>
     <row r="53">
@@ -1041,10 +1041,10 @@
         </is>
       </c>
       <c r="B53">
-        <v>-0.447999951450762</v>
+        <v>-1.162283858586717</v>
       </c>
       <c r="C53">
-        <v>-0.2787463632046948</v>
+        <v>0.05630708598483475</v>
       </c>
     </row>
     <row r="54">
@@ -1054,10 +1054,10 @@
         </is>
       </c>
       <c r="B54">
-        <v>0.7162508111534631</v>
+        <v>-1.118832267866769</v>
       </c>
       <c r="C54">
-        <v>-0.4472009829641315</v>
+        <v>-0.1781197834615124</v>
       </c>
     </row>
     <row r="55">
@@ -1067,10 +1067,10 @@
         </is>
       </c>
       <c r="B55">
-        <v>-1.043876877984581</v>
+        <v>1.280160583798384</v>
       </c>
       <c r="C55">
-        <v>0.1384388301847229</v>
+        <v>-0.7337942731944935</v>
       </c>
     </row>
     <row r="56">
@@ -1080,10 +1080,10 @@
         </is>
       </c>
       <c r="B56">
-        <v>0.327469247630051</v>
+        <v>-1.687716547444067</v>
       </c>
       <c r="C56">
-        <v>1.530244704346299</v>
+        <v>0.0677357128789724</v>
       </c>
     </row>
     <row r="57">
@@ -1093,10 +1093,10 @@
         </is>
       </c>
       <c r="B57">
-        <v>-1.014264343303722</v>
+        <v>-0.3101160021036893</v>
       </c>
       <c r="C57">
-        <v>-1.037778346821457</v>
+        <v>0.03844145976173567</v>
       </c>
     </row>
     <row r="58">
@@ -1106,10 +1106,10 @@
         </is>
       </c>
       <c r="B58">
-        <v>0.6350569065028411</v>
+        <v>0.02722691789023859</v>
       </c>
       <c r="C58">
-        <v>-1.430404080126029</v>
+        <v>-0.5273997448312344</v>
       </c>
     </row>
     <row r="59">
@@ -1119,10 +1119,10 @@
         </is>
       </c>
       <c r="B59">
-        <v>1.374791906334585</v>
+        <v>0.1566254622282821</v>
       </c>
       <c r="C59">
-        <v>1.458972193832134</v>
+        <v>0.3260174511970322</v>
       </c>
     </row>
     <row r="60">
@@ -1132,10 +1132,10 @@
         </is>
       </c>
       <c r="B60">
-        <v>0.9649993796852292</v>
+        <v>0.3369107290609449</v>
       </c>
       <c r="C60">
-        <v>1.535048512987729</v>
+        <v>1.645753955539954</v>
       </c>
     </row>
     <row r="61">
@@ -1145,10 +1145,10 @@
         </is>
       </c>
       <c r="B61">
-        <v>1.641442874292939</v>
+        <v>0.2051649363366351</v>
       </c>
       <c r="C61">
-        <v>1.196965705853907</v>
+        <v>0.2726756292393743</v>
       </c>
     </row>
     <row r="62">
@@ -1158,10 +1158,10 @@
         </is>
       </c>
       <c r="B62">
-        <v>0.09180604470551501</v>
+        <v>1.910246214772641</v>
       </c>
       <c r="C62">
-        <v>-0.7237200160406063</v>
+        <v>1.388923440040703</v>
       </c>
     </row>
     <row r="63">
@@ -1171,10 +1171,10 @@
         </is>
       </c>
       <c r="B63">
-        <v>-0.286293864411994</v>
+        <v>0.344997686045916</v>
       </c>
       <c r="C63">
-        <v>0.160024321399692</v>
+        <v>-0.3696005706628843</v>
       </c>
     </row>
     <row r="64">
@@ -1184,10 +1184,10 @@
         </is>
       </c>
       <c r="B64">
-        <v>-1.334830230182506</v>
+        <v>-0.2354944050818674</v>
       </c>
       <c r="C64">
-        <v>-0.5368722670347509</v>
+        <v>0.0364162416751474</v>
       </c>
     </row>
     <row r="65">
@@ -1197,10 +1197,10 @@
         </is>
       </c>
       <c r="B65">
-        <v>0.7150823376468762</v>
+        <v>-0.5569357669631262</v>
       </c>
       <c r="C65">
-        <v>-0.8887849473214948</v>
+        <v>1.073767010660213</v>
       </c>
     </row>
     <row r="66">
@@ -1210,10 +1210,10 @@
         </is>
       </c>
       <c r="B66">
-        <v>-1.190634953354629</v>
+        <v>-2.24577494911594</v>
       </c>
       <c r="C66">
-        <v>-0.9450948241039698</v>
+        <v>-1.047310846731992</v>
       </c>
     </row>
     <row r="67">
@@ -1223,10 +1223,10 @@
         </is>
       </c>
       <c r="B67">
-        <v>-0.7916039536350002</v>
+        <v>1.538143610461958</v>
       </c>
       <c r="C67">
-        <v>-0.8480520342138722</v>
+        <v>1.365272658221671</v>
       </c>
     </row>
     <row r="68">
@@ -1236,10 +1236,10 @@
         </is>
       </c>
       <c r="B68">
-        <v>-0.07984233941405737</v>
+        <v>-1.707627178870643</v>
       </c>
       <c r="C68">
-        <v>0.7199122149168419</v>
+        <v>-0.5099398938139079</v>
       </c>
     </row>
     <row r="69">
@@ -1249,10 +1249,10 @@
         </is>
       </c>
       <c r="B69">
-        <v>-0.01944364489452329</v>
+        <v>-1.933031609157011</v>
       </c>
       <c r="C69">
-        <v>-0.2937595799586871</v>
+        <v>-0.03345644778969281</v>
       </c>
     </row>
     <row r="70">
@@ -1262,10 +1262,10 @@
         </is>
       </c>
       <c r="B70">
-        <v>-1.015492437412829</v>
+        <v>0.2150795234041116</v>
       </c>
       <c r="C70">
-        <v>0.2164932020639055</v>
+        <v>-0.5976008189764208</v>
       </c>
     </row>
     <row r="71">
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="B71">
-        <v>1.017134339663054</v>
+        <v>0.7576309025038536</v>
       </c>
       <c r="C71">
-        <v>-1.228347058738174</v>
+        <v>0.9226795165766183</v>
       </c>
     </row>
     <row r="72">
@@ -1288,10 +1288,10 @@
         </is>
       </c>
       <c r="B72">
-        <v>-0.5651156820602669</v>
+        <v>1.908599446358915</v>
       </c>
       <c r="C72">
-        <v>-0.496062552548176</v>
+        <v>0.7521617941841506</v>
       </c>
     </row>
     <row r="73">
@@ -1301,10 +1301,10 @@
         </is>
       </c>
       <c r="B73">
-        <v>-0.07627819160269328</v>
+        <v>-0.8454256056825156</v>
       </c>
       <c r="C73">
-        <v>-0.9863522879508551</v>
+        <v>0.3272661944136094</v>
       </c>
     </row>
     <row r="74">
@@ -1314,10 +1314,10 @@
         </is>
       </c>
       <c r="B74">
-        <v>-1.442639072499371</v>
+        <v>0.1246854629886674</v>
       </c>
       <c r="C74">
-        <v>0.7357827993012916</v>
+        <v>0.5458057453628739</v>
       </c>
     </row>
     <row r="75">
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="B75">
-        <v>-0.08539611836730553</v>
+        <v>-0.8387064420090813</v>
       </c>
       <c r="C75">
-        <v>-0.6121249165963846</v>
+        <v>-1.110477198892787</v>
       </c>
     </row>
     <row r="76">
@@ -1340,10 +1340,10 @@
         </is>
       </c>
       <c r="B76">
-        <v>0.7699150328136748</v>
+        <v>1.928470342783749</v>
       </c>
       <c r="C76">
-        <v>0.5186763785175618</v>
+        <v>1.689324882013162</v>
       </c>
     </row>
     <row r="77">
@@ -1353,10 +1353,10 @@
         </is>
       </c>
       <c r="B77">
-        <v>0.9182350197684939</v>
+        <v>0.917801199510739</v>
       </c>
       <c r="C77">
-        <v>1.643540392477553</v>
+        <v>1.350874263616676</v>
       </c>
     </row>
     <row r="78">
@@ -1366,10 +1366,10 @@
         </is>
       </c>
       <c r="B78">
-        <v>0.1918966814766843</v>
+        <v>1.613320746834939</v>
       </c>
       <c r="C78">
-        <v>1.06151607260803</v>
+        <v>-0.3596806969315776</v>
       </c>
     </row>
     <row r="79">
@@ -1379,10 +1379,10 @@
         </is>
       </c>
       <c r="B79">
-        <v>-0.6786317439674235</v>
+        <v>-1.214222496421239</v>
       </c>
       <c r="C79">
-        <v>-1.20312245849742</v>
+        <v>0.213715229197539</v>
       </c>
     </row>
     <row r="80">
@@ -1392,10 +1392,10 @@
         </is>
       </c>
       <c r="B80">
-        <v>-0.8080465338734393</v>
+        <v>2.125994925046566</v>
       </c>
       <c r="C80">
-        <v>-1.210110813608355</v>
+        <v>1.761360325203373</v>
       </c>
     </row>
     <row r="81">
@@ -1405,10 +1405,10 @@
         </is>
       </c>
       <c r="B81">
-        <v>-1.069994962662308</v>
+        <v>-0.7101102808672408</v>
       </c>
       <c r="C81">
-        <v>-0.9801410799507591</v>
+        <v>-0.7918908202905997</v>
       </c>
     </row>
     <row r="82">
@@ -1418,10 +1418,10 @@
         </is>
       </c>
       <c r="B82">
-        <v>0.2626908126907877</v>
+        <v>-0.2484107369377444</v>
       </c>
       <c r="C82">
-        <v>1.032015869731991</v>
+        <v>-0.24156592000753</v>
       </c>
     </row>
     <row r="83">
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="B83">
-        <v>0.6547285642817857</v>
+        <v>-1.11229246610793</v>
       </c>
       <c r="C83">
-        <v>0.04477060111823522</v>
+        <v>-0.02180055348836135</v>
       </c>
     </row>
     <row r="84">
@@ -1444,10 +1444,10 @@
         </is>
       </c>
       <c r="B84">
-        <v>2.091562288460097</v>
+        <v>-0.5105429987021128</v>
       </c>
       <c r="C84">
-        <v>3.417736220637384</v>
+        <v>-1.129574528368031</v>
       </c>
     </row>
     <row r="85">
@@ -1457,10 +1457,10 @@
         </is>
       </c>
       <c r="B85">
-        <v>0.6742735457465352</v>
+        <v>1.506882484566397</v>
       </c>
       <c r="C85">
-        <v>-0.6795086554154153</v>
+        <v>1.307931234193524</v>
       </c>
     </row>
     <row r="86">
@@ -1470,10 +1470,10 @@
         </is>
       </c>
       <c r="B86">
-        <v>0.9194417680084362</v>
+        <v>0.8647113010017322</v>
       </c>
       <c r="C86">
-        <v>-0.6232679721687795</v>
+        <v>0.5659248558738297</v>
       </c>
     </row>
     <row r="87">
@@ -1483,10 +1483,10 @@
         </is>
       </c>
       <c r="B87">
-        <v>1.0529464434959</v>
+        <v>0.1669762580776529</v>
       </c>
       <c r="C87">
-        <v>1.065574942076886</v>
+        <v>-0.8964783395350115</v>
       </c>
     </row>
     <row r="88">
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="B88">
-        <v>0.9666789450153581</v>
+        <v>0.9629370487105808</v>
       </c>
       <c r="C88">
-        <v>1.403047316173785</v>
+        <v>0.4580324218327248</v>
       </c>
     </row>
     <row r="89">
@@ -1509,10 +1509,10 @@
         </is>
       </c>
       <c r="B89">
-        <v>-1.672248835763473</v>
+        <v>0.5410592323703121</v>
       </c>
       <c r="C89">
-        <v>0.2275369065368016</v>
+        <v>0.5814287378373704</v>
       </c>
     </row>
     <row r="90">
@@ -1522,10 +1522,10 @@
         </is>
       </c>
       <c r="B90">
-        <v>-1.883680170214981</v>
+        <v>-0.4361036172060931</v>
       </c>
       <c r="C90">
-        <v>-1.294129374175912</v>
+        <v>1.691375076128206</v>
       </c>
     </row>
     <row r="91">
@@ -1535,10 +1535,10 @@
         </is>
       </c>
       <c r="B91">
-        <v>0.8696334452018231</v>
+        <v>-0.4380241561089502</v>
       </c>
       <c r="C91">
-        <v>-0.01720926761022923</v>
+        <v>0.5559076991710745</v>
       </c>
     </row>
     <row r="92">
@@ -1548,10 +1548,10 @@
         </is>
       </c>
       <c r="B92">
-        <v>0.2219157899405297</v>
+        <v>1.318133636537172</v>
       </c>
       <c r="C92">
-        <v>-0.8669949162722318</v>
+        <v>1.524278885631464</v>
       </c>
     </row>
     <row r="93">
@@ -1561,10 +1561,10 @@
         </is>
       </c>
       <c r="B93">
-        <v>1.945805320489005</v>
+        <v>-0.3830317391711996</v>
       </c>
       <c r="C93">
-        <v>0.4305155872819852</v>
+        <v>-1.276929103648588</v>
       </c>
     </row>
     <row r="94">
@@ -1574,10 +1574,10 @@
         </is>
       </c>
       <c r="B94">
-        <v>-0.9341010211220775</v>
+        <v>1.538936709179313</v>
       </c>
       <c r="C94">
-        <v>0.339975917390932</v>
+        <v>1.381244876457683</v>
       </c>
     </row>
     <row r="95">
@@ -1587,10 +1587,10 @@
         </is>
       </c>
       <c r="B95">
-        <v>-0.3147876953816148</v>
+        <v>-0.5831569283203301</v>
       </c>
       <c r="C95">
-        <v>0.04518050945900132</v>
+        <v>-0.9557193583296394</v>
       </c>
     </row>
     <row r="96">
@@ -1600,10 +1600,10 @@
         </is>
       </c>
       <c r="B96">
-        <v>0.7425436954887178</v>
+        <v>-0.7214249344506125</v>
       </c>
       <c r="C96">
-        <v>-0.2942118140435927</v>
+        <v>-0.0846552004807436</v>
       </c>
     </row>
     <row r="97">
@@ -1613,10 +1613,10 @@
         </is>
       </c>
       <c r="B97">
-        <v>-1.161810186005471</v>
+        <v>-1.083010146769169</v>
       </c>
       <c r="C97">
-        <v>0.299547352676221</v>
+        <v>-1.793155162055067</v>
       </c>
     </row>
     <row r="98">
@@ -1626,10 +1626,10 @@
         </is>
       </c>
       <c r="B98">
-        <v>-1.318647348428341</v>
+        <v>-0.6616510413026295</v>
       </c>
       <c r="C98">
-        <v>-1.622218098220021</v>
+        <v>0.2256711850521072</v>
       </c>
     </row>
     <row r="99">
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="B99">
-        <v>0.9579731337718439</v>
+        <v>-0.7357611057486512</v>
       </c>
       <c r="C99">
-        <v>-1.131772758777606</v>
+        <v>-0.01290639209236694</v>
       </c>
     </row>
     <row r="100">
@@ -1652,10 +1652,10 @@
         </is>
       </c>
       <c r="B100">
-        <v>0.07327338870083749</v>
+        <v>1.654125497548368</v>
       </c>
       <c r="C100">
-        <v>-0.2614710404911583</v>
+        <v>1.748820100501547</v>
       </c>
     </row>
     <row r="101">
@@ -1665,10 +1665,1310 @@
         </is>
       </c>
       <c r="B101">
-        <v>-0.6613461783682937</v>
+        <v>2.176116774595378</v>
       </c>
       <c r="C101">
-        <v>1.541256749188422</v>
+        <v>1.180130578276483</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="B102">
+        <v>-1.999252292339516</v>
+      </c>
+      <c r="C102">
+        <v>0.2836896155600365</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="B103">
+        <v>0.5719386387454188</v>
+      </c>
+      <c r="C103">
+        <v>-1.077252293735859</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="B104">
+        <v>0.1480766127762503</v>
+      </c>
+      <c r="C104">
+        <v>-0.101098274344065</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="B105">
+        <v>1.097078010765099</v>
+      </c>
+      <c r="C105">
+        <v>1.361903313451561</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="B106">
+        <v>1.310501817993315</v>
+      </c>
+      <c r="C106">
+        <v>-1.343845803051729</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="B107">
+        <v>-1.463267588712357</v>
+      </c>
+      <c r="C107">
+        <v>-0.2695092716149632</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="B108">
+        <v>0.5984220307983485</v>
+      </c>
+      <c r="C108">
+        <v>2.198517031733465</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="B109">
+        <v>1.086694000933332</v>
+      </c>
+      <c r="C109">
+        <v>-0.1279177606573114</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="B110">
+        <v>1.324358996902526</v>
+      </c>
+      <c r="C110">
+        <v>1.107046211753218</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="B111">
+        <v>-1.062112756890238</v>
+      </c>
+      <c r="C111">
+        <v>-1.751334658189969</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="B112">
+        <v>1.222260191739456</v>
+      </c>
+      <c r="C112">
+        <v>0.7876359203916247</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="B113">
+        <v>0.1528567681981692</v>
+      </c>
+      <c r="C113">
+        <v>0.3613301110956096</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="B114">
+        <v>-0.1820264116182219</v>
+      </c>
+      <c r="C114">
+        <v>-1.082009645339918</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="B115">
+        <v>-0.9084587353530755</v>
+      </c>
+      <c r="C115">
+        <v>-0.2010867098361563</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="B116">
+        <v>3.572594092461649</v>
+      </c>
+      <c r="C116">
+        <v>1.497678428958472</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="B117">
+        <v>1.197171828352951</v>
+      </c>
+      <c r="C117">
+        <v>0.6341532312550228</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="B118">
+        <v>-1.122464853253133</v>
+      </c>
+      <c r="C118">
+        <v>-1.802410535895852</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="B119">
+        <v>-0.1879431899683206</v>
+      </c>
+      <c r="C119">
+        <v>1.352104060891843</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="B120">
+        <v>-0.07420740409054626</v>
+      </c>
+      <c r="C120">
+        <v>-2.531027189342265</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="B121">
+        <v>0.757842318292687</v>
+      </c>
+      <c r="C121">
+        <v>0.2829853916925027</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="B122">
+        <v>-0.81596842523865</v>
+      </c>
+      <c r="C122">
+        <v>0.3253247787105026</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="B123">
+        <v>2.626272628324566</v>
+      </c>
+      <c r="C123">
+        <v>-0.9952811582816423</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="B124">
+        <v>-0.3500018875043035</v>
+      </c>
+      <c r="C124">
+        <v>-1.26398121223906</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="B125">
+        <v>1.016527146923534</v>
+      </c>
+      <c r="C125">
+        <v>0.5126260642453777</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="B126">
+        <v>0.6101215630718436</v>
+      </c>
+      <c r="C126">
+        <v>-0.251651017697156</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="B127">
+        <v>-0.02224730649868606</v>
+      </c>
+      <c r="C127">
+        <v>-0.490204567756189</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="B128">
+        <v>-0.9943327246064831</v>
+      </c>
+      <c r="C128">
+        <v>-0.1209058078232716</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="B129">
+        <v>-0.1938150217089517</v>
+      </c>
+      <c r="C129">
+        <v>0.0886135600751333</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="B130">
+        <v>-0.6056861438169707</v>
+      </c>
+      <c r="C130">
+        <v>-1.135735454925431</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="B131">
+        <v>-2.340107622928218</v>
+      </c>
+      <c r="C131">
+        <v>-0.448867247025578</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="B132">
+        <v>-1.580906782072291</v>
+      </c>
+      <c r="C132">
+        <v>-1.073287847542883</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="B133">
+        <v>-0.4845357315824217</v>
+      </c>
+      <c r="C133">
+        <v>0.3842518454606656</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>133</t>
+        </is>
+      </c>
+      <c r="B134">
+        <v>-0.02352246703898592</v>
+      </c>
+      <c r="C134">
+        <v>0.3302062750113058</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="B135">
+        <v>-0.6778095285687836</v>
+      </c>
+      <c r="C135">
+        <v>0.8394896119066586</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="B136">
+        <v>0.7438458609555165</v>
+      </c>
+      <c r="C136">
+        <v>0.5348338149391845</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="B137">
+        <v>-0.4525967839045762</v>
+      </c>
+      <c r="C137">
+        <v>0.4486002006495707</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="B138">
+        <v>-0.2691356596354444</v>
+      </c>
+      <c r="C138">
+        <v>1.475909059664989</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="B139">
+        <v>-0.4899196114535729</v>
+      </c>
+      <c r="C139">
+        <v>0.6228072220725827</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="B140">
+        <v>-0.7260118052434218</v>
+      </c>
+      <c r="C140">
+        <v>-0.6571529504674539</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="B141">
+        <v>0.9432211356251257</v>
+      </c>
+      <c r="C141">
+        <v>1.049822912749397</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="B142">
+        <v>-0.5564777521908374</v>
+      </c>
+      <c r="C142">
+        <v>-0.507007494429754</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="B143">
+        <v>-2.479884882553896</v>
+      </c>
+      <c r="C143">
+        <v>-1.66818174131706</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="B144">
+        <v>-0.4334843989161373</v>
+      </c>
+      <c r="C144">
+        <v>1.786017904260743</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="B145">
+        <v>0.2544078579912308</v>
+      </c>
+      <c r="C145">
+        <v>0.828576455728409</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="B146">
+        <v>-1.178181179981191</v>
+      </c>
+      <c r="C146">
+        <v>-2.376822296250518</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="B147">
+        <v>-0.6811835556024948</v>
+      </c>
+      <c r="C147">
+        <v>-1.345505524845561</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="B148">
+        <v>-0.2606693890433986</v>
+      </c>
+      <c r="C148">
+        <v>0.6068986263223314</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="B149">
+        <v>-0.5507978600705306</v>
+      </c>
+      <c r="C149">
+        <v>1.10452194766168</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="B150">
+        <v>0.5537124430167799</v>
+      </c>
+      <c r="C150">
+        <v>0.8860791853579293</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="B151">
+        <v>-0.7093053581983249</v>
+      </c>
+      <c r="C151">
+        <v>-1.714766750772316</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="B152">
+        <v>-0.3537767430127707</v>
+      </c>
+      <c r="C152">
+        <v>0.518597234192839</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="B153">
+        <v>0.1745729359407287</v>
+      </c>
+      <c r="C153">
+        <v>-0.2022311837354357</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="B154">
+        <v>1.123842677789486</v>
+      </c>
+      <c r="C154">
+        <v>0.3362502991460341</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="B155">
+        <v>1.468481617927371</v>
+      </c>
+      <c r="C155">
+        <v>0.485866698745421</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="B156">
+        <v>-1.030212078087672</v>
+      </c>
+      <c r="C156">
+        <v>-1.38979721100606</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="B157">
+        <v>-0.203356819000886</v>
+      </c>
+      <c r="C157">
+        <v>-0.2685198670321156</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="B158">
+        <v>-1.313300892928851</v>
+      </c>
+      <c r="C158">
+        <v>-0.3907224095473326</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="B159">
+        <v>-0.8259902985457075</v>
+      </c>
+      <c r="C159">
+        <v>-1.076660027109202</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="B160">
+        <v>-0.4590941672845291</v>
+      </c>
+      <c r="C160">
+        <v>-0.06431358245552934</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="B161">
+        <v>0.0686481458330704</v>
+      </c>
+      <c r="C161">
+        <v>-0.6438645484836427</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="B162">
+        <v>-0.309201816285965</v>
+      </c>
+      <c r="C162">
+        <v>0.2949270366309413</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="B163">
+        <v>-0.1212309603204541</v>
+      </c>
+      <c r="C163">
+        <v>0.8685073537718337</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="B164">
+        <v>1.657766406613995</v>
+      </c>
+      <c r="C164">
+        <v>1.721272066887826</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="B165">
+        <v>1.9957760440635</v>
+      </c>
+      <c r="C165">
+        <v>0.9703919182835813</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="B166">
+        <v>2.201399271437821</v>
+      </c>
+      <c r="C166">
+        <v>0.2442203324897102</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>166</t>
+        </is>
+      </c>
+      <c r="B167">
+        <v>1.019571300711692</v>
+      </c>
+      <c r="C167">
+        <v>-0.1156628574655613</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="B168">
+        <v>-0.9376110153210961</v>
+      </c>
+      <c r="C168">
+        <v>-0.7951927200801042</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="B169">
+        <v>0.954120872215325</v>
+      </c>
+      <c r="C169">
+        <v>0.2070716132946708</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>169</t>
+        </is>
+      </c>
+      <c r="B170">
+        <v>-0.8976185401308191</v>
+      </c>
+      <c r="C170">
+        <v>0.2276567938870218</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="B171">
+        <v>-0.3203893869914433</v>
+      </c>
+      <c r="C171">
+        <v>1.320937957419434</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="B172">
+        <v>1.075006086978612</v>
+      </c>
+      <c r="C172">
+        <v>1.134616663694415</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="B173">
+        <v>0.5176095859885707</v>
+      </c>
+      <c r="C173">
+        <v>-0.7219544555023983</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="B174">
+        <v>3.117097253063018</v>
+      </c>
+      <c r="C174">
+        <v>1.004049664064436</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="B175">
+        <v>-1.728205599958308</v>
+      </c>
+      <c r="C175">
+        <v>0.3785878103517538</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="B176">
+        <v>-0.1775388738317563</v>
+      </c>
+      <c r="C176">
+        <v>-1.184044953801701</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="B177">
+        <v>-0.8218398281683431</v>
+      </c>
+      <c r="C177">
+        <v>0.2098189538844389</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="B178">
+        <v>0.0259235218753918</v>
+      </c>
+      <c r="C178">
+        <v>-0.02777070834471082</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="B179">
+        <v>1.145267907927876</v>
+      </c>
+      <c r="C179">
+        <v>1.754332546994564</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="B180">
+        <v>-0.4750137414291525</v>
+      </c>
+      <c r="C180">
+        <v>1.013848450725882</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="B181">
+        <v>0.4695342578933525</v>
+      </c>
+      <c r="C181">
+        <v>-0.5944320868213538</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="B182">
+        <v>0.3758676620152151</v>
+      </c>
+      <c r="C182">
+        <v>-0.0247899189530329</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="B183">
+        <v>-1.619869957744527</v>
+      </c>
+      <c r="C183">
+        <v>-1.59269890994275</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="B184">
+        <v>-0.2252296890853233</v>
+      </c>
+      <c r="C184">
+        <v>-0.440505740474982</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="B185">
+        <v>1.694236217351489</v>
+      </c>
+      <c r="C185">
+        <v>1.001908838718879</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="B186">
+        <v>-0.3446071932033832</v>
+      </c>
+      <c r="C186">
+        <v>-0.3715483811734843</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="B187">
+        <v>-1.262682170339158</v>
+      </c>
+      <c r="C187">
+        <v>-1.205657604526719</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="B188">
+        <v>0.1156849304735015</v>
+      </c>
+      <c r="C188">
+        <v>0.6743707596951718</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="B189">
+        <v>1.082062652939848</v>
+      </c>
+      <c r="C189">
+        <v>2.074863566604589</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="B190">
+        <v>-0.9997642271452684</v>
+      </c>
+      <c r="C190">
+        <v>-0.9358005342336759</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="B191">
+        <v>-1.877479799287276</v>
+      </c>
+      <c r="C191">
+        <v>-0.578000254382839</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="B192">
+        <v>0.00544291082569484</v>
+      </c>
+      <c r="C192">
+        <v>-0.007293729018909102</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="B193">
+        <v>1.752550076452104</v>
+      </c>
+      <c r="C193">
+        <v>0.09751319034802253</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="B194">
+        <v>-0.5258230936740502</v>
+      </c>
+      <c r="C194">
+        <v>-0.8778571691289718</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="B195">
+        <v>0.3108163100187875</v>
+      </c>
+      <c r="C195">
+        <v>-0.03003221429507424</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="B196">
+        <v>0.2991105972444726</v>
+      </c>
+      <c r="C196">
+        <v>0.9163172580077811</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="B197">
+        <v>0.1804493359901827</v>
+      </c>
+      <c r="C197">
+        <v>-0.9874042927997124</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="B198">
+        <v>-0.04813787743246234</v>
+      </c>
+      <c r="C198">
+        <v>-1.897341592314779</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="B199">
+        <v>0.2812364164896841</v>
+      </c>
+      <c r="C199">
+        <v>0.8830935461767734</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>199</t>
+        </is>
+      </c>
+      <c r="B200">
+        <v>-0.6605126627170355</v>
+      </c>
+      <c r="C200">
+        <v>-0.4571340899789917</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="B201">
+        <v>2.21089621303082</v>
+      </c>
+      <c r="C201">
+        <v>-0.4891861477152164</v>
       </c>
     </row>
   </sheetData>
